--- a/AI_Audit_Log_NguyenThanhQuan.xlsx
+++ b/AI_Audit_Log_NguyenThanhQuan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_Uni\SU_26\SWD392\ai-audit-log-123-WaanTh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607184E9-10FD-4AD1-BD0E-F4ACFD946872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE84C10F-EFC0-44DF-9C05-AEB03F15AD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
   <si>
     <t>STT</t>
   </si>
@@ -167,12 +167,40 @@
 • Decision Ownership: Quyết định gắn nhãn primary/secondary nhất quán: người dùng là primary cho UC họ chủ động khởi tạo; external service (OpenAI, Email) luôn là secondary.
 EVIDENCE: Diagram UC Forum và UC VIP với các actor được gắn nhãn đúng vai trò trong báo cáo Week 2.</t>
   </si>
+  <si>
+    <t>"Liệt kê các lớp chính cần có trong một hệ thống quản lý học tập trực tuyến theo chuẩn Class Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê: User, Course, Lesson, Quiz, Result.
+Quyết định: Thiếu phân biệt entity/control/boundary. Tôi bổ sung thêm lớp Enrollment và tách AuthService thành control class riêng.</t>
+  </si>
+  <si>
+    <t>"Hãy xác định các quan hệ giữa các lớp: User, Order, Product, Payment trong một hệ thống bán hàng."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chỉ dùng Association cho tất cả các quan hệ.
+Kiểm chứng: Thiếu sót. Tôi phân tích lại: Order–Product là Aggregation, Order–Payment là Composition vì Payment không tồn tại nếu không có Order.</t>
+  </si>
+  <si>
+    <t>"Trong class diagram, khi nào nên dùng Inheritance thay vì Association để thể hiện quan hệ giữa hai lớp?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI khuyên dùng Inheritance khi hai lớp "có liên quan đến nhau".
+Kiểm chứng: Đây là Hallucination. Tôi xác nhận lại: chỉ dùng Inheritance khi thỏa mãn quan hệ "is-a", còn lại dùng Association.</t>
+  </si>
+  <si>
+    <t>"Xây dựng các bước để thiết kế Class Diagram từ đặc tả yêu cầu (SRS) cho một dự án phần mềm."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất: đọc SRS → tìm danh từ → vẽ class → thêm method.
+Quyết định: Tôi bổ sung bước kiểm tra multiplicity và xác nhận quan hệ với team trước khi finalize diagram.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +241,19 @@
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -262,10 +303,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -312,9 +354,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{6E74C894-89AD-41A3-8677-3549374BE672}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -847,9 +896,86 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AI_Audit_Log_NguyenThanhQuan.xlsx
+++ b/AI_Audit_Log_NguyenThanhQuan.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_Uni\SU_26\SWD392\ai-audit-log-123-WaanTh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE84C10F-EFC0-44DF-9C05-AEB03F15AD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1832D650-EDB0-47D4-AA1E-7E45E51FB1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
   <si>
     <t>STT</t>
   </si>
@@ -194,6 +195,34 @@
   <si>
     <t>Phản hồi: AI đề xuất: đọc SRS → tìm danh từ → vẽ class → thêm method.
 Quyết định: Tôi bổ sung bước kiểm tra multiplicity và xác nhận quan hệ với team trước khi finalize diagram.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả Sequence Diagram là biểu đồ thể hiện sự tương tác giữa các đối tượng theo trình tự thời gian, gồm lifeline, message và activation bar.
+Quyết định: Tôi giữ định nghĩa này và yêu cầu AI lấy thêm ví dụ thực tế với UC "Login" để dễ hình dung hơn.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê: Actor, Lifeline, Message, Activation Bar, Return Message, Combined Fragment.
+Kiểm chứng: Đủ các thành phần cơ bản. Tôi bổ sung thêm "Boundary/Guard Condition" vì AI bỏ sót yếu tố quan trọng khi dùng alt/loop fragment.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI khẳng định mọi quan hệ &lt;&lt;include&gt;&gt; trong Use Case đều phải vẽ thành một message riêng trong Sequence Diagram.
+Kiểm chứng: Đây là Hallucination. Tôi xác nhận lại: Sequence Diagram thể hiện luồng thực thi thực tế, không cần ánh xạ 1-1 với quan hệ UC. Một message call có thể bao hàm cả hành vi included.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất: xác định actor → liệt kê object → vẽ message theo thứ tự → thêm return message.
+Quyết định: Tôi bổ sung bước "xác định combined fragment (alt/loop/opt)" và "kiểm tra nhất quán với Class Diagram" trước khi finalize, vì AI bỏ qua hai bước kiểm tra quan trọng này.</t>
+  </si>
+  <si>
+    <t>"Sequence Diagram là gì? Giải thích ngắn gọn cho người mới học UML."</t>
+  </si>
+  <si>
+    <t>"Hãy liệt kê các thành phần chính cần có trong một Sequence Diagram theo chuẩn UML 2.x."</t>
+  </si>
+  <si>
+    <t>"Khi nào nên dùng &lt;&lt;include&gt;&gt; trong Use Case và khi nào nên thể hiện nó bằng message call trong Sequence Diagram?"</t>
+  </si>
+  <si>
+    <t>"Xây dựng các bước để vẽ Sequence Diagram từ một Use Case đã có sẵn."</t>
   </si>
 </sst>
 </file>
@@ -264,7 +293,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -302,12 +331,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -359,6 +403,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -978,4 +1037,90 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0306AA51-9969-41F4-8E66-6D7EB33052D9}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="20">
+        <v>2</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="20">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="20">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI_Audit_Log_NguyenThanhQuan.xlsx
+++ b/AI_Audit_Log_NguyenThanhQuan.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_Uni\SU_26\SWD392\ai-audit-log-123-WaanTh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1832D650-EDB0-47D4-AA1E-7E45E51FB1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B80B860-28B9-4C61-91D9-4E1B0BE95D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
   <si>
     <t>STT</t>
   </si>
@@ -224,18 +225,53 @@
   <si>
     <t>"Xây dựng các bước để vẽ Sequence Diagram từ một Use Case đã có sẵn."</t>
   </si>
+  <si>
+    <t>"Giải thích ngắn gọn State Diagram là gì và dùng khi nào trong UML."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả State Diagram thể hiện các trạng thái của một đối tượng và sự chuyển đổi giữa chúng khi có sự kiện xảy ra.
+Quyết định: Tôi giữ định nghĩa này và yêu cầu AI cho ví dụ thực tế với đối tượng "Order" trong hệ thống bán hàng để dễ hình dung hơn.</t>
+  </si>
+  <si>
+    <t>"Hãy liệt kê các thành phần chính trong một State Diagram theo chuẩn UML 2.x."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê: Initial State, Final State, State, Transition, Event, Guard Condition, Action.
+Kiểm chứng: Đủ thành phần cơ bản. Tôi bổ sung "Composite State" vì AI bỏ sót trường hợp trạng thái lồng nhau quan trọng trong hệ thống phức tạp.</t>
+  </si>
+  <si>
+    <t>"State Diagram và Activity Diagram khác nhau như thế nào? Khi nào dùng cái nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI khẳng định hai loại có thể dùng thay thế nhau hoàn toàn.
+Kiểm chứng: Đây là Hallucination. Tôi xác nhận lại: State Diagram mô tả vòng đời của một đối tượng cụ thể; Activity Diagram mô tả luồng xử lý/quy trình nghiệp vụ. Không thể thay thế nhau.</t>
+  </si>
+  <si>
+    <t>"Xây dựng các bước để vẽ State Diagram cho đối tượng Submission trong hệ thống IELTSPhobic."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất: xác định đối tượng → liệt kê trạng thái → xác định sự kiện → vẽ transition.
+Quyết định: Tôi bổ sung bước "xác định guard condition" và "kiểm tra tính nhất quán với Sequence Diagram" vì AI bỏ sót hai bước kiểm tra quan trọng này.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -349,9 +385,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -359,7 +395,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -368,56 +404,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1123,4 +1183,90 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FCA6706-20BB-451D-B4D1-F7D7286ECCBC}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="24">
+        <v>2</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
+        <v>3</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="24">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI_Audit_Log_NguyenThanhQuan.xlsx
+++ b/AI_Audit_Log_NguyenThanhQuan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_Uni\SU_26\SWD392\ai-audit-log-123-WaanTh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B80B860-28B9-4C61-91D9-4E1B0BE95D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B252B73F-C945-43DD-B072-9D03ECC3F5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,15 @@
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="85">
   <si>
     <t>STT</t>
   </si>
@@ -253,18 +255,124 @@
     <t>Phản hồi: AI đề xuất: xác định đối tượng → liệt kê trạng thái → xác định sự kiện → vẽ transition.
 Quyết định: Tôi bổ sung bước "xác định guard condition" và "kiểm tra tính nhất quán với Sequence Diagram" vì AI bỏ sót hai bước kiểm tra quan trọng này.</t>
   </si>
+  <si>
+    <t>State-dependent Dynamic Modeling</t>
+  </si>
+  <si>
+    <t>"State Diagram là gì và được sử dụng để làm gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích State Diagram mô tả các trạng thái của đối tượng và các sự kiện làm thay đổi trạng thái.
+Kiểm chứng: Tôi đối chiếu với slide bài học.
+Quyết định: Sử dụng State Diagram để mô hình hóa trạng thái của Ticket.</t>
+  </si>
+  <si>
+    <t>Xác định đối tượng</t>
+  </si>
+  <si>
+    <t>"Đối tượng nào trong Smart Queue Management System nên có State Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Ticket vì đối tượng này thay đổi trạng thái theo thời gian.
+Kiểm chứng: Đối chiếu với nghiệp vụ hệ thống.
+Quyết định: Chọn Ticket để xây dựng State Diagram.</t>
+  </si>
+  <si>
+    <t>Initial State</t>
+  </si>
+  <si>
+    <t>"Trạng thái ban đầu của Ticket là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất trạng thái Created sau khi khách hàng lấy số thứ tự.
+Kiểm chứng: So sánh với quy trình nghiệp vụ.
+Quyết định: Chọn Created là trạng thái đầu tiên.</t>
+  </si>
+  <si>
+    <t>State Identification</t>
+  </si>
+  <si>
+    <t>"Ticket có thể trải qua những trạng thái nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Created, Waiting, Called, Serving, Completed và Cancelled.
+Kiểm chứng: Đối chiếu với Use Case của nhóm.
+Quyết định: Áp dụng các trạng thái này vào sơ đồ.</t>
+  </si>
+  <si>
+    <t>Component Diagram</t>
+  </si>
+  <si>
+    <t>"Component Diagram là gì và được sử dụng trong giai đoạn nào của UML?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Component Diagram mô tả kiến trúc vật lý của hệ thống, thể hiện các module phần mềm và mối quan hệ giữa chúng.
+Kiểm chứng: Tôi đối chiếu với slide bài học về Component Diagram.
+Quyết định: Sử dụng Component Diagram để mô tả kiến trúc của dự án nhóm.</t>
+  </si>
+  <si>
+    <t>Xác định Component</t>
+  </si>
+  <si>
+    <t>"Đối với Smart Queue Management System Using AI, hệ thống nên có những component nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các component như Mobile App, Web Dashboard, Queue Management Service, AI Prediction Service, Notification Service và Database.
+Kiểm chứng: Tôi đối chiếu với kiến trúc hệ thống mà nhóm đã xây dựng.
+Quyết định: Chọn các component phù hợp để đưa vào sơ đồ.</t>
+  </si>
+  <si>
+    <t>Front-end Component</t>
+  </si>
+  <si>
+    <t>"Frontend của hệ thống nên được biểu diễn như thế nào trong Component Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất tách thành Mobile App và Admin Dashboard vì phục vụ hai nhóm người dùng khác nhau.
+Kiểm chứng: So sánh với yêu cầu của dự án.
+Quyết định: Tách Front-end thành hai component riêng.</t>
+  </si>
+  <si>
+    <t>Backend Component</t>
+  </si>
+  <si>
+    <t>"Backend nên chia thành những component nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Queue Service, User Service, AI Service và Notification Service để tăng tính mô-đun.
+Kiểm chứng: Đối chiếu với kiến trúc backend của nhóm.
+Quyết định: Thiết kế backend theo các service độc lập.</t>
+  </si>
+  <si>
+    <t>AI Component</t>
+  </si>
+  <si>
+    <t>"AI Prediction Service có vai trò gì trong Component Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích component này nhận dữ liệu hàng chờ và dự đoán thời gian chờ để gửi kết quả cho Queue Service.
+Kiểm chứng: Đối chiếu với chức năng AI của dự án.
+Quyết định: Thêm AI Prediction Service vào Component Diagram.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -385,9 +493,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -395,7 +503,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -404,80 +512,95 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1269,4 +1392,188 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BB02CC-D572-442E-82CA-C4DC262408E7}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="38.44140625" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" customWidth="1"/>
+    <col min="4" max="4" width="47" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5005F7A3-CD1F-4693-9348-502CD86EC53C}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="39.44140625" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>